--- a/output/看屋檢查清單_新北建案_2026-10-09_六_財務評估.xlsx
+++ b/output/看屋檢查清單_新北建案_2026-10-09_六_財務評估.xlsx
@@ -231,7 +231,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>資料搜尋日期：2026-10-09　|　來源：591／樂居／樂屋網／5168／住展／Mobile01／建商官網／政府圖資　|　【試算】貸8成30年2.321%（央行統計2026/8五大銀行新承做平均，7月為2.29%）；新青安3.0自2026/8/1上路，一段式機動利率1.775%起、上限1000萬，第4年起補貼遞減、第6年期滿｜稅費≒總價1~1.5%｜保固：結構15年、設備1年（自交屋起）｜履約保證法定五擇一｜斷層：北盆地僅山腳斷層(第二類)　|　【現場確認】＝公開資料查無，須向代銷索取或調謄本　|　查詢：土壤液化 liquid.net.tw／soil.taipei；淹水 dmap.ncdr.nat.gov.tw；新北液化圖資第1期板橋三重等、第2期中和土城新店等　|　治安為網路整理之113年新北各區犯罪率分級，非警政署原表　|　!＝風險提醒　+＝正面條件（原⚠️／✅）</t>
+          <t>資料搜尋日期：2026-10-09　|　來源：591／樂居／樂屋網／5168／住展／Mobile01／建商官網／政府圖資　|　【試算】貸8成30年2.321%（央行統計2026/8五大銀行新承做平均，7月為2.29%）；新青安3.0自2026/8/1上路，一段式機動利率1.775%起、上限1000萬，第4年起補貼遞減、第6年期滿｜稅費≒總價1~1.5%｜保固：結構15年、設備1年（自交屋起）｜履約保證法定五擇一｜斷層：北盆地僅山腳斷層(第二類)　|　【現場確認】＝公開資料查無，須向代銷索取或調謄本　|　查詢：土壤液化 liquid.net.tw／soil.taipei；淹水 dmap.ncdr.nat.gov.tw；新北液化圖資第1期板橋三重等、第2期中和土城新店等　|　治安為網路整理之113年新北各區犯罪率分級，非警政署原表　|　!＝風險提醒　+＝正面條件（原⚠️／✅）；實登：ToEstate(至2026-07)</t>
         </is>
       </c>
     </row>
@@ -379,48 +379,46 @@
       <c r="C6" s="8" t="inlineStr">
         <is>
           <t>開價75~88萬/坪
-實際成交約73.7~76萬/坪</t>
+近1年中位71.9萬；1房中位78.5萬(P25~P75 77.3~79.9萬)</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>開價62~70萬/坪（另有來源記59~70萬）
-實際成交約67~69.1萬/坪，區間59.0~72.8萬</t>
+          <t>開價62~70萬/坪
+實登中位66.2萬(P25~P75 64.4~67.6萬)；近6月68.4萬</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>全案成交約65.7~67.9萬/坪
-!新推期別已站上73~83萬/坪，與全案均價落差逾15萬，看屋須先確認是哪一期</t>
+          <t>II紐約公園成交約66~69萬/坪
+III巴黎公園／4英倫公園預售83~85萬/坪
+!期別落差逾15萬</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>實登2026-08更新：68~85萬/坪
-實際成交約75~79.7萬/坪
-!Mobile01有「單坪破80萬」討論串，高樓層已突破開價上緣</t>
+          <t>實登P25~P75 73.6~78.1萬/坪，近6月77.3萬
+!土城區預售中位70.6萬，本案偏高</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>近期成交約88.3~89萬/坪（四平台一致）
-區間65.55~103.47萬/坪；早期開價70~85萬/坪
-!為七案中單價次高，僅次於將捷MRT</t>
+          <t>近1年中位89.7萬/坪；歷年65.5~110.7萬
+!為七案中單價最高</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>開價86~91萬/坪（樂居記87~98萬）
-實際成交76.4~90.9萬/坪，各平台均價82~85.4萬
-!仍為七案中單價最高者</t>
+          <t>開價86~91萬/坪
+實登P25~P75 81.3~84.4萬，低於開價約3~9%
+!單價僅次於文德好境</t>
         </is>
       </c>
       <c r="I6" s="8" t="inlineStr">
         <is>
-          <t>實際成交均價約75~76萬/坪（591/5168一致）
-5168成交區間54.57~95.42萬/坪（09-25另見的58~62萬屬低價尾端）
+          <t>全期中位61.2萬，近6月78.5萬/坪(漲幅明顯)
 開價約76~86萬/坪
-+成交價低於開價約4~12%，議價空間為七案中較明確者</t>
++附近新案參考價85.9萬，本案仍偏低</t>
         </is>
       </c>
     </row>
